--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/pre LAM_HRM-2031-0480/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/pre LAM_HRM-2031-0480/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.3273</v>
+        <v>17.24821</v>
       </c>
       <c r="D2" t="n">
-        <v>17.28977</v>
+        <v>17.10021</v>
       </c>
       <c r="E2" t="n">
-        <v>16.82828</v>
+        <v>17.16318</v>
       </c>
       <c r="F2" t="n">
-        <v>43.78929</v>
+        <v>43.95809</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05274</v>
+        <v>0.05255</v>
       </c>
       <c r="H2" t="n">
-        <v>1.87051</v>
+        <v>1.86416</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.3546</v>
+        <v>17.21936</v>
       </c>
       <c r="D3" t="n">
-        <v>16.97383</v>
+        <v>16.69823</v>
       </c>
       <c r="E3" t="n">
-        <v>17.28708</v>
+        <v>17.19679</v>
       </c>
       <c r="F3" t="n">
-        <v>44.32594</v>
+        <v>42.8357</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05263</v>
+        <v>0.05182</v>
       </c>
       <c r="H3" t="n">
-        <v>1.88072</v>
+        <v>1.88221</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.24718</v>
+        <v>17.35627</v>
       </c>
       <c r="D4" t="n">
-        <v>17.18894</v>
+        <v>16.91509</v>
       </c>
       <c r="E4" t="n">
-        <v>17.22039</v>
+        <v>17.14858</v>
       </c>
       <c r="F4" t="n">
-        <v>44.15308</v>
+        <v>43.77844</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05203</v>
+        <v>0.05238</v>
       </c>
       <c r="H4" t="n">
-        <v>1.86576</v>
+        <v>1.82866</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.82561</v>
+        <v>17.46423</v>
       </c>
       <c r="D6" t="n">
-        <v>16.59014</v>
+        <v>16.21637</v>
       </c>
       <c r="E6" t="n">
-        <v>16.87424</v>
+        <v>17.02178</v>
       </c>
       <c r="F6" t="n">
-        <v>22.21313</v>
+        <v>22.47326</v>
       </c>
       <c r="G6" t="n">
-        <v>35.48369</v>
+        <v>36.04484</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.83337</v>
+        <v>17.37712</v>
       </c>
       <c r="D7" t="n">
-        <v>16.62433</v>
+        <v>16.02662</v>
       </c>
       <c r="E7" t="n">
-        <v>16.7845</v>
+        <v>17.17352</v>
       </c>
       <c r="F7" t="n">
-        <v>22.84534</v>
+        <v>22.94486</v>
       </c>
       <c r="G7" t="n">
-        <v>35.57403</v>
+        <v>35.15962</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.20877</v>
+        <v>16.92563</v>
       </c>
       <c r="D8" t="n">
-        <v>16.19981</v>
+        <v>16.64628</v>
       </c>
       <c r="E8" t="n">
-        <v>17.18295</v>
+        <v>16.69203</v>
       </c>
       <c r="F8" t="n">
-        <v>22.40638</v>
+        <v>22.64626</v>
       </c>
       <c r="G8" t="n">
-        <v>35.43747</v>
+        <v>35.65278</v>
       </c>
     </row>
   </sheetData>
